--- a/从零开始学Slots/从零开始学Slots-26-数值篇-ExpandingWild(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-26-数值篇-ExpandingWild(1).xlsx
@@ -9778,6 +9778,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:L172" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -11920,5 +11923,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:P120" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-26-数值篇-ExpandingWild(1).xlsx
+++ b/从零开始学Slots/从零开始学Slots-26-数值篇-ExpandingWild(1).xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="218">
   <si>
     <r>
       <rPr>
@@ -8656,7 +8656,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8791,6 +8791,22 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -9847,8 +9863,8 @@
       <c r="B5" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>121</v>
+      <c r="C5" s="34">
+        <v>5</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -9967,120 +9983,120 @@
       <c r="A15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>142</v>
+      <c r="B15" s="35">
+        <v>9</v>
+      </c>
+      <c r="C15" s="35">
+        <v>9</v>
+      </c>
+      <c r="D15" s="35">
+        <v>9</v>
+      </c>
+      <c r="E15" s="35">
+        <v>9</v>
+      </c>
+      <c r="F15" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>142</v>
+      <c r="B16" s="35">
+        <v>9</v>
+      </c>
+      <c r="C16" s="35">
+        <v>9</v>
+      </c>
+      <c r="D16" s="35">
+        <v>9</v>
+      </c>
+      <c r="E16" s="35">
+        <v>9</v>
+      </c>
+      <c r="F16" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>142</v>
+      <c r="B17" s="35">
+        <v>9</v>
+      </c>
+      <c r="C17" s="35">
+        <v>9</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E17" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>142</v>
+      <c r="E17" s="35">
+        <v>9</v>
+      </c>
+      <c r="F17" s="35">
+        <v>9</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>144</v>
+      <c r="B18" s="35">
+        <v>10</v>
+      </c>
+      <c r="C18" s="35">
+        <v>10</v>
+      </c>
+      <c r="D18" s="35">
+        <v>10</v>
+      </c>
+      <c r="E18" s="35">
+        <v>10</v>
+      </c>
+      <c r="F18" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="E19" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>144</v>
+      <c r="B19" s="35">
+        <v>10</v>
+      </c>
+      <c r="C19" s="35">
+        <v>10</v>
+      </c>
+      <c r="D19" s="35">
+        <v>10</v>
+      </c>
+      <c r="E19" s="35">
+        <v>10</v>
+      </c>
+      <c r="F19" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>144</v>
+      <c r="B20" s="35">
+        <v>10</v>
+      </c>
+      <c r="C20" s="35">
+        <v>10</v>
+      </c>
+      <c r="D20" s="35">
+        <v>10</v>
+      </c>
+      <c r="E20" s="35">
+        <v>10</v>
+      </c>
+      <c r="F20" s="35">
+        <v>10</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10330,8 +10346,8 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
-        <v>142</v>
+      <c r="A34" s="36">
+        <v>9</v>
       </c>
       <c r="B34" s="18" t="n">
         <f aca="false">COUNTIF(B15:B29,"9")</f>
@@ -10362,8 +10378,8 @@
       </c>
     </row>
     <row r="35" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
-        <v>144</v>
+      <c r="A35" s="36">
+        <v>10</v>
       </c>
       <c r="B35" s="18" t="n">
         <f aca="false">COUNTIF(B15:B29,"10")</f>
@@ -10591,8 +10607,8 @@
       <c r="A44" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B44" s="20" t="s">
-        <v>142</v>
+      <c r="B44" s="36">
+        <v>9</v>
       </c>
       <c r="C44" s="21" t="n">
         <v>3</v>
@@ -10617,8 +10633,8 @@
       <c r="A45" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="B45" s="20" t="s">
-        <v>144</v>
+      <c r="B45" s="36">
+        <v>10</v>
       </c>
       <c r="C45" s="21" t="n">
         <v>3</v>
@@ -10721,8 +10737,8 @@
       <c r="A49" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="B49" s="20" t="s">
-        <v>142</v>
+      <c r="B49" s="36">
+        <v>9</v>
       </c>
       <c r="C49" s="21" t="n">
         <v>3</v>
@@ -10747,8 +10763,8 @@
       <c r="A50" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="B50" s="20" t="s">
-        <v>144</v>
+      <c r="B50" s="36">
+        <v>10</v>
       </c>
       <c r="C50" s="21" t="n">
         <v>3</v>
@@ -10851,8 +10867,8 @@
       <c r="A54" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B54" s="20" t="s">
-        <v>142</v>
+      <c r="B54" s="36">
+        <v>9</v>
       </c>
       <c r="C54" s="21" t="n">
         <v>3</v>
@@ -10877,8 +10893,8 @@
       <c r="A55" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="B55" s="20" t="s">
-        <v>144</v>
+      <c r="B55" s="36">
+        <v>10</v>
       </c>
       <c r="C55" s="21" t="n">
         <v>3</v>
@@ -11006,40 +11022,40 @@
       <c r="A62" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B62" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="F62" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="G62" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="H62" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="I62" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="J62" s="23" t="s">
-        <v>191</v>
+      <c r="B62" s="37">
+        <v>3</v>
+      </c>
+      <c r="C62" s="37">
+        <v>4</v>
+      </c>
+      <c r="D62" s="37">
+        <v>5</v>
+      </c>
+      <c r="E62" s="37">
+        <v>3</v>
+      </c>
+      <c r="F62" s="37">
+        <v>4</v>
+      </c>
+      <c r="G62" s="37">
+        <v>5</v>
+      </c>
+      <c r="H62" s="37">
+        <v>3</v>
+      </c>
+      <c r="I62" s="37">
+        <v>4</v>
+      </c>
+      <c r="J62" s="37">
+        <v>5</v>
       </c>
       <c r="K62" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20" t="s">
-        <v>142</v>
+      <c r="A63" s="36">
+        <v>9</v>
       </c>
       <c r="B63" s="18" t="n">
         <f aca="false">(C44+$C$43)*(D44+$D$43)*(E44+$E$43)*($B$8-(F44+$F$43))*$B$8</f>
@@ -11076,8 +11092,8 @@
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20" t="s">
-        <v>144</v>
+      <c r="A64" s="36">
+        <v>10</v>
       </c>
       <c r="B64" s="18" t="n">
         <f aca="false">(C45+$C$43)*(D45+$D$43)*(E45+$E$43)*($B$8-(F45+$F$43))*$B$8</f>
@@ -11252,40 +11268,40 @@
       <c r="A70" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B70" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="H70" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="I70" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="J70" s="23" t="s">
-        <v>191</v>
+      <c r="B70" s="37">
+        <v>3</v>
+      </c>
+      <c r="C70" s="37">
+        <v>4</v>
+      </c>
+      <c r="D70" s="37">
+        <v>5</v>
+      </c>
+      <c r="E70" s="37">
+        <v>3</v>
+      </c>
+      <c r="F70" s="37">
+        <v>4</v>
+      </c>
+      <c r="G70" s="37">
+        <v>5</v>
+      </c>
+      <c r="H70" s="37">
+        <v>3</v>
+      </c>
+      <c r="I70" s="37">
+        <v>4</v>
+      </c>
+      <c r="J70" s="37">
+        <v>5</v>
       </c>
       <c r="K70" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="20" t="s">
-        <v>142</v>
+      <c r="A71" s="36">
+        <v>9</v>
       </c>
       <c r="B71" s="18" t="n">
         <f aca="false">(C49+$C$43)*(D49+$D$43)*(E49+$E$43)*($B$8-(F49+$F$43))*$B$8</f>
@@ -11322,8 +11338,8 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20" t="s">
-        <v>144</v>
+      <c r="A72" s="36">
+        <v>10</v>
       </c>
       <c r="B72" s="18" t="n">
         <f aca="false">(C50+$C$43)*(D50+$D$43)*(E50+$E$43)*($B$8-(F50+$F$43))*$B$8</f>
@@ -11498,40 +11514,40 @@
       <c r="A78" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="B78" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="C78" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="F78" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="G78" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="H78" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="I78" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="J78" s="23" t="s">
-        <v>191</v>
+      <c r="B78" s="37">
+        <v>3</v>
+      </c>
+      <c r="C78" s="37">
+        <v>4</v>
+      </c>
+      <c r="D78" s="37">
+        <v>5</v>
+      </c>
+      <c r="E78" s="37">
+        <v>3</v>
+      </c>
+      <c r="F78" s="37">
+        <v>4</v>
+      </c>
+      <c r="G78" s="37">
+        <v>5</v>
+      </c>
+      <c r="H78" s="37">
+        <v>3</v>
+      </c>
+      <c r="I78" s="37">
+        <v>4</v>
+      </c>
+      <c r="J78" s="37">
+        <v>5</v>
       </c>
       <c r="K78" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="20" t="s">
-        <v>142</v>
+      <c r="A79" s="36">
+        <v>9</v>
       </c>
       <c r="B79" s="18" t="n">
         <f aca="false">(C54+$C$43)*(D54+$D$43)*(E54+$E$43)*($B$8-(F54+$F$43))*$B$8</f>
@@ -11568,8 +11584,8 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="20" t="s">
-        <v>144</v>
+      <c r="A80" s="36">
+        <v>10</v>
       </c>
       <c r="B80" s="18" t="n">
         <f aca="false">(C55+$C$43)*(D55+$D$43)*(E55+$E$43)*($B$8-(F55+$F$43))*$B$8</f>
